--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N88_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N88_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>66.26947854930549</v>
+        <v>10.76879026426214</v>
       </c>
       <c r="D2" t="n">
-        <v>50.73369954057812</v>
+        <v>8.244226175343943</v>
       </c>
       <c r="E2" t="n">
-        <v>9.535270481706132</v>
+        <v>1.549481453277247</v>
       </c>
       <c r="F2" t="n">
-        <v>14.16519400541929</v>
+        <v>2.301844025880635</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>57.82601305758303</v>
+        <v>9.396727121857243</v>
       </c>
       <c r="D3" t="n">
-        <v>47.16558767643924</v>
+        <v>7.664407997421377</v>
       </c>
       <c r="E3" t="n">
-        <v>9.535270481706132</v>
+        <v>1.549481453277247</v>
       </c>
       <c r="F3" t="n">
-        <v>14.16519400541929</v>
+        <v>2.301844025880635</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>52.33592604837035</v>
+        <v>8.504587982860182</v>
       </c>
       <c r="D4" t="n">
-        <v>36.50320111690694</v>
+        <v>5.931770181497378</v>
       </c>
       <c r="E4" t="n">
-        <v>9.535270481706132</v>
+        <v>1.549481453277247</v>
       </c>
       <c r="F4" t="n">
-        <v>14.16519400541929</v>
+        <v>2.301844025880635</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>41.17360436535733</v>
+        <v>6.690710709370566</v>
       </c>
       <c r="D5" t="n">
-        <v>41.22937285977024</v>
+        <v>6.699773089712665</v>
       </c>
       <c r="E5" t="n">
-        <v>9.535270481706132</v>
+        <v>1.549481453277247</v>
       </c>
       <c r="F5" t="n">
-        <v>14.16519400541929</v>
+        <v>2.301844025880635</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>37.10898379805504</v>
+        <v>6.030209867183943</v>
       </c>
       <c r="D6" t="n">
-        <v>5.725811307007661</v>
+        <v>0.930444337388745</v>
       </c>
       <c r="E6" t="n">
-        <v>9.535270481706132</v>
+        <v>1.549481453277247</v>
       </c>
       <c r="F6" t="n">
-        <v>14.16519400541929</v>
+        <v>2.301844025880635</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>42.57735183713624</v>
+        <v>6.91881967353464</v>
       </c>
       <c r="D7" t="n">
-        <v>44.38930115666724</v>
+        <v>7.213261437958427</v>
       </c>
       <c r="E7" t="n">
-        <v>9.535270481706132</v>
+        <v>1.549481453277247</v>
       </c>
       <c r="F7" t="n">
-        <v>14.16519400541929</v>
+        <v>2.301844025880635</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>46.67164818360442</v>
+        <v>7.584142829835718</v>
       </c>
       <c r="D8" t="n">
-        <v>46.27521822913209</v>
+        <v>7.519722962233964</v>
       </c>
       <c r="E8" t="n">
-        <v>9.535270481706132</v>
+        <v>1.549481453277247</v>
       </c>
       <c r="F8" t="n">
-        <v>14.16519400541929</v>
+        <v>2.301844025880635</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
